--- a/priv/python/excel_templates/TEMPLATE_EOW Report.xlsx
+++ b/priv/python/excel_templates/TEMPLATE_EOW Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deanerfree/projects/elixir/suncor-project-spinup/priv/python/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D17D76-664C-B14B-A81E-D77338CB2323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23674C9-7C68-5C41-87D0-BAB1AA7967B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="660" windowWidth="22780" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,7 +355,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -676,21 +676,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -727,7 +712,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -879,24 +864,10 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,44 +1264,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="64" t="s">
+      <c r="K1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="73" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="74"/>
+      <c r="G2" s="70"/>
       <c r="H2" s="38" t="s">
         <v>5</v>
       </c>
@@ -1338,30 +1309,30 @@
         <v>55</v>
       </c>
       <c r="J2" s="1"/>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="66"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="65" t="s">
+      <c r="L2" s="62"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="67"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="63"/>
       <c r="S2" s="37" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
       <c r="H3" s="52"/>
       <c r="I3" s="43"/>
       <c r="J3" s="1"/>
@@ -1489,10 +1460,10 @@
       <c r="B6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="69"/>
+      <c r="D6" s="65"/>
       <c r="E6" s="11" t="s">
         <v>31</v>
       </c>
@@ -1559,15 +1530,25 @@
       <c r="S7" s="5"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="53">
-        <v>1</v>
-      </c>
-      <c r="B8" s="29"/>
+      <c r="A8" s="53" t="str">
+        <f t="shared" ref="A8:A9" si="0">IF(E8, A7+1, "")</f>
+        <v/>
+      </c>
+      <c r="B8" s="29" t="str">
+        <f t="shared" ref="B8:B9" si="1">IF(F8="","",IF(F8&gt;3, IF(F8&gt;=3.3, 3, 2), IF(F8&lt;1.5, 1, 2)))</f>
+        <v/>
+      </c>
       <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
+      <c r="D8" s="31" t="str">
+        <f>IF(E8="","",C8+E8)</f>
+        <v/>
+      </c>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
+      <c r="G8" s="31" t="str">
+        <f t="shared" ref="G8:G9" si="2">IF(E8=0,"",(F8/E8*100))</f>
+        <v/>
+      </c>
       <c r="H8" s="45"/>
       <c r="I8" s="54"/>
       <c r="J8" s="1"/>
@@ -1584,25 +1565,55 @@
       <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="53"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
+      <c r="A9" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B9" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C9" s="31" t="str">
+        <f t="shared" ref="C9" si="3">IF(E9, D8, "")</f>
+        <v/>
+      </c>
+      <c r="D9" s="31" t="str">
+        <f t="shared" ref="D8:D9" si="4">IF(E9="","",D8+E9)</f>
+        <v/>
+      </c>
       <c r="E9" s="31"/>
       <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
+      <c r="G9" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H9" s="45"/>
       <c r="I9" s="54"/>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="53"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
+      <c r="A10" s="53" t="str">
+        <f t="shared" ref="A10:A73" si="5">IF(E10, A9+1, "")</f>
+        <v/>
+      </c>
+      <c r="B10" s="29" t="str">
+        <f t="shared" ref="B10:B73" si="6">IF(F10="","",IF(F10&gt;3, IF(F10&gt;=3.3, 3, 2), IF(F10&lt;1.5, 1, 2)))</f>
+        <v/>
+      </c>
+      <c r="C10" s="31" t="str">
+        <f t="shared" ref="C10:C73" si="7">IF(E10, D9, "")</f>
+        <v/>
+      </c>
+      <c r="D10" s="31" t="str">
+        <f t="shared" ref="D10:D73" si="8">IF(E10="","",D9+E10)</f>
+        <v/>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
+      <c r="G10" s="31" t="str">
+        <f t="shared" ref="G10:G73" si="9">IF(E10=0,"",(F10/E10*100))</f>
+        <v/>
+      </c>
       <c r="H10" s="44"/>
       <c r="I10" s="54"/>
       <c r="J10" s="1"/>
@@ -1611,948 +1622,2223 @@
       <c r="R10" s="50"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" s="53"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="A11" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B11" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C11" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D11" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="E11" s="31"/>
       <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
+      <c r="G11" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H11" s="44"/>
       <c r="I11" s="54"/>
       <c r="J11" s="1"/>
       <c r="P11" s="9"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="53"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="31"/>
+      <c r="A12" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B12" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C12" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D12" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H12" s="45"/>
       <c r="I12" s="54"/>
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:19" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="53"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
+      <c r="A13" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B13" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C13" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D13" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H13" s="45"/>
       <c r="I13" s="54"/>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" s="53"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="31"/>
+      <c r="A14" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B14" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C14" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D14" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H14" s="44"/>
       <c r="I14" s="54"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="53"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
+      <c r="A15" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B15" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C15" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D15" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H15" s="44"/>
       <c r="I15" s="54"/>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:19" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="53"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31"/>
+      <c r="A16" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B16" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C16" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D16" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H16" s="45"/>
       <c r="I16" s="54"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="53"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
+      <c r="A17" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B17" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C17" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D17" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H17" s="45"/>
       <c r="I17" s="54"/>
       <c r="M17" s="9"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="53"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
+      <c r="A18" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B18" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C18" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D18" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H18" s="45"/>
       <c r="I18" s="54"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="53"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="31"/>
+      <c r="A19" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B19" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C19" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D19" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H19" s="45"/>
       <c r="I19" s="54"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="53"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="31"/>
+      <c r="A20" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B20" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C20" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D20" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H20" s="44"/>
       <c r="I20" s="54"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="53"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
+      <c r="A21" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B21" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C21" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D21" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H21" s="44"/>
       <c r="I21" s="54"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="53"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="31"/>
+      <c r="A22" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B22" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C22" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D22" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H22" s="44"/>
       <c r="I22" s="54"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="53"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="31"/>
+      <c r="A23" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B23" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C23" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D23" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H23" s="44"/>
       <c r="I23" s="54"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="53"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="31"/>
+      <c r="A24" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B24" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C24" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D24" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H24" s="44"/>
       <c r="I24" s="54"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="53"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="31"/>
+      <c r="A25" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B25" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C25" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D25" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H25" s="44"/>
       <c r="I25" s="54"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="53"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
+      <c r="A26" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B26" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C26" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D26" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H26" s="44"/>
       <c r="I26" s="54"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="53"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="31"/>
+      <c r="A27" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B27" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C27" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D27" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H27" s="44"/>
       <c r="I27" s="54"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="53"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="31"/>
+      <c r="A28" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B28" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C28" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D28" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H28" s="44"/>
       <c r="I28" s="54"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="53"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="31"/>
+      <c r="A29" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B29" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C29" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D29" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H29" s="45"/>
       <c r="I29" s="54"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="53"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="31"/>
+      <c r="A30" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B30" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C30" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D30" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H30" s="44"/>
       <c r="I30" s="54"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="53"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="31"/>
+      <c r="A31" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B31" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C31" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D31" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H31" s="44"/>
       <c r="I31" s="54"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="53"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
+      <c r="A32" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B32" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C32" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D32" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H32" s="44"/>
       <c r="I32" s="54"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="53"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="31"/>
+      <c r="A33" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B33" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C33" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D33" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H33" s="44"/>
       <c r="I33" s="54"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="53"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
+      <c r="A34" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B34" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C34" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D34" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H34" s="44"/>
       <c r="I34" s="54"/>
     </row>
     <row r="35" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="53"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31"/>
+      <c r="A35" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B35" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C35" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D35" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H35" s="45"/>
       <c r="I35" s="54"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="53"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
+      <c r="A36" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B36" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C36" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D36" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H36" s="45"/>
       <c r="I36" s="54"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="53"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="31"/>
+      <c r="A37" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B37" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C37" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D37" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H37" s="45"/>
       <c r="I37" s="54"/>
     </row>
     <row r="38" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="53"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="31"/>
+      <c r="A38" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B38" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C38" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D38" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H38" s="45"/>
       <c r="I38" s="54"/>
     </row>
     <row r="39" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="53"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="31"/>
+      <c r="A39" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B39" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C39" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D39" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H39" s="45"/>
       <c r="I39" s="54"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="53"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="31"/>
+      <c r="A40" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B40" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C40" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D40" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H40" s="45"/>
       <c r="I40" s="54"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="53"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="31"/>
+      <c r="A41" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B41" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C41" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D41" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H41" s="45"/>
       <c r="I41" s="54"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="53"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="31"/>
+      <c r="A42" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B42" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C42" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D42" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H42" s="45"/>
       <c r="I42" s="54"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="53"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="31"/>
+      <c r="A43" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B43" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C43" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D43" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H43" s="45"/>
       <c r="I43" s="54"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="53"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="31"/>
+      <c r="A44" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B44" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C44" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D44" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H44" s="45"/>
       <c r="I44" s="54"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" s="53"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="31"/>
+      <c r="A45" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B45" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C45" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D45" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H45" s="45"/>
       <c r="I45" s="54"/>
     </row>
     <row r="46" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="53"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="31"/>
+      <c r="A46" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B46" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C46" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D46" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H46" s="45"/>
       <c r="I46" s="54"/>
     </row>
     <row r="47" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="53"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="31"/>
+      <c r="A47" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B47" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C47" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D47" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H47" s="45"/>
       <c r="I47" s="54"/>
     </row>
     <row r="48" spans="1:9" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="53"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="31"/>
+      <c r="A48" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B48" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C48" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D48" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H48" s="45"/>
       <c r="I48" s="54"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="53"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="31"/>
+      <c r="A49" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B49" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C49" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D49" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H49" s="45"/>
       <c r="I49" s="54"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="53"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="31"/>
+      <c r="A50" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B50" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C50" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D50" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H50" s="45"/>
       <c r="I50" s="54"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="53"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="31"/>
+      <c r="A51" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B51" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C51" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D51" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H51" s="45"/>
       <c r="I51" s="54"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="53"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="31"/>
+      <c r="A52" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B52" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C52" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D52" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H52" s="45"/>
       <c r="I52" s="54"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="53"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="31"/>
+      <c r="A53" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B53" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C53" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D53" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H53" s="44"/>
       <c r="I53" s="54"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="53"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="31"/>
+      <c r="A54" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B54" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C54" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D54" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H54" s="45"/>
       <c r="I54" s="54"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="53"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="31"/>
+      <c r="A55" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B55" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C55" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D55" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H55" s="45"/>
       <c r="I55" s="54"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="53"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="31"/>
+      <c r="A56" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B56" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C56" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D56" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E56" s="31"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H56" s="45"/>
       <c r="I56" s="54"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="53"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="31"/>
+      <c r="A57" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B57" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C57" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D57" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H57" s="45"/>
       <c r="I57" s="54"/>
     </row>
     <row r="58" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="53"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="31"/>
+      <c r="A58" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B58" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C58" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D58" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H58" s="45"/>
       <c r="I58" s="54"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="53"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="31"/>
+      <c r="A59" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B59" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C59" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D59" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H59" s="45"/>
       <c r="I59" s="54"/>
     </row>
     <row r="60" spans="1:14" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="53"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="31"/>
+      <c r="A60" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B60" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C60" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D60" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H60" s="46"/>
       <c r="I60" s="54"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="53"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="31"/>
+      <c r="A61" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B61" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C61" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D61" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H61" s="44"/>
       <c r="I61" s="54"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" s="53"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="31"/>
+      <c r="A62" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B62" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C62" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D62" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E62" s="31"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H62" s="44"/>
       <c r="I62" s="54"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="53"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="31"/>
+      <c r="A63" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B63" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C63" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D63" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E63" s="31"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H63" s="45"/>
       <c r="I63" s="54"/>
       <c r="N63" s="9"/>
     </row>
     <row r="64" spans="1:14" ht="137.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="53"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="31"/>
+      <c r="A64" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B64" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C64" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D64" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H64" s="49"/>
       <c r="I64" s="54"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="53"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="31"/>
+      <c r="A65" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B65" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C65" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D65" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H65" s="45"/>
       <c r="I65" s="54"/>
     </row>
     <row r="66" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="53"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="31"/>
+      <c r="A66" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B66" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C66" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D66" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H66" s="45"/>
       <c r="I66" s="54"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="53"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="31"/>
+      <c r="A67" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B67" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C67" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D67" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H67" s="45"/>
       <c r="I67" s="54"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="53"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="31"/>
+      <c r="A68" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B68" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C68" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D68" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E68" s="31"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H68" s="45"/>
       <c r="I68" s="54"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="53"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="31"/>
+      <c r="A69" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B69" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C69" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D69" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H69" s="45"/>
       <c r="I69" s="54"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="53"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="31"/>
+      <c r="A70" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B70" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C70" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D70" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H70" s="46"/>
       <c r="I70" s="54"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="53"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="31"/>
+      <c r="A71" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B71" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C71" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D71" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H71" s="46"/>
       <c r="I71" s="54"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="53"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="31"/>
+      <c r="A72" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B72" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C72" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D72" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H72" s="46"/>
       <c r="I72" s="54"/>
     </row>
     <row r="73" spans="1:9" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="53"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="31"/>
+      <c r="A73" s="53" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B73" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="C73" s="31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="D73" s="31" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
       <c r="H73" s="46"/>
       <c r="I73" s="54"/>
     </row>
     <row r="74" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="53"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="31"/>
+      <c r="A74" s="53" t="str">
+        <f t="shared" ref="A74:A95" si="10">IF(E74, A73+1, "")</f>
+        <v/>
+      </c>
+      <c r="B74" s="29" t="str">
+        <f t="shared" ref="B74:B95" si="11">IF(F74="","",IF(F74&gt;3, IF(F74&gt;=3.3, 3, 2), IF(F74&lt;1.5, 1, 2)))</f>
+        <v/>
+      </c>
+      <c r="C74" s="31" t="str">
+        <f t="shared" ref="C74:C95" si="12">IF(E74, D73, "")</f>
+        <v/>
+      </c>
+      <c r="D74" s="31" t="str">
+        <f t="shared" ref="D74:D95" si="13">IF(E74="","",D73+E74)</f>
+        <v/>
+      </c>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31" t="str">
+        <f t="shared" ref="G74:G95" si="14">IF(E74=0,"",(F74/E74*100))</f>
+        <v/>
+      </c>
       <c r="H74" s="46"/>
       <c r="I74" s="54"/>
     </row>
     <row r="75" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="53"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="31"/>
+      <c r="A75" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B75" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C75" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D75" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H75" s="46"/>
       <c r="I75" s="54"/>
     </row>
     <row r="76" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="53"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="31"/>
-      <c r="D76" s="31"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="31"/>
+      <c r="A76" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B76" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C76" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D76" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H76" s="46"/>
       <c r="I76" s="54"/>
     </row>
     <row r="77" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="53"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="31"/>
+      <c r="A77" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B77" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C77" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D77" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H77" s="46"/>
       <c r="I77" s="54"/>
     </row>
     <row r="78" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="53"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="31"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
-      <c r="G78" s="31"/>
+      <c r="A78" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B78" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C78" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D78" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H78" s="46"/>
       <c r="I78" s="54"/>
     </row>
     <row r="79" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="31"/>
+      <c r="A79" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B79" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C79" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D79" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H79" s="46"/>
       <c r="I79" s="54"/>
     </row>
     <row r="80" spans="1:9" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="31"/>
-      <c r="D80" s="31"/>
-      <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="31"/>
+      <c r="A80" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B80" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C80" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D80" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H80" s="46"/>
       <c r="I80" s="54"/>
     </row>
     <row r="81" spans="1:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="53"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="31"/>
-      <c r="D81" s="31"/>
-      <c r="E81" s="30"/>
-      <c r="F81" s="30"/>
-      <c r="G81" s="31"/>
+      <c r="A81" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B81" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C81" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D81" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H81" s="46"/>
       <c r="I81" s="54"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A82" s="53"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="31"/>
-      <c r="D82" s="31"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="31"/>
+      <c r="A82" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B82" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C82" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D82" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H82" s="46"/>
       <c r="I82" s="54"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" s="53"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="31"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
-      <c r="G83" s="31"/>
+      <c r="A83" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B83" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C83" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D83" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H83" s="46"/>
       <c r="I83" s="54"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A84" s="53"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="31"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="31"/>
+      <c r="A84" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B84" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C84" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D84" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E84" s="31"/>
+      <c r="F84" s="31"/>
+      <c r="G84" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H84" s="46"/>
       <c r="I84" s="54"/>
     </row>
     <row r="85" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="53"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="30"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="31"/>
+      <c r="A85" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B85" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C85" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D85" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E85" s="31"/>
+      <c r="F85" s="31"/>
+      <c r="G85" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H85" s="46"/>
       <c r="I85" s="54"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A86" s="53"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="31"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="31"/>
+      <c r="A86" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B86" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C86" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D86" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E86" s="31"/>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H86" s="46"/>
       <c r="I86" s="54"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A87" s="53"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="31"/>
+      <c r="A87" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B87" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C87" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D87" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H87" s="46"/>
       <c r="I87" s="54"/>
     </row>
     <row r="88" spans="1:9" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="53"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="31"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="31"/>
+      <c r="A88" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B88" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C88" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D88" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E88" s="31"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H88" s="46"/>
       <c r="I88" s="54"/>
     </row>
     <row r="89" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="53"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="30"/>
-      <c r="F89" s="30"/>
-      <c r="G89" s="31"/>
+      <c r="A89" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B89" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C89" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D89" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E89" s="31"/>
+      <c r="F89" s="31"/>
+      <c r="G89" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H89" s="46"/>
       <c r="I89" s="54"/>
     </row>
     <row r="90" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="53"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="31"/>
-      <c r="D90" s="31"/>
-      <c r="E90" s="30"/>
-      <c r="F90" s="30"/>
-      <c r="G90" s="31"/>
+      <c r="A90" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B90" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C90" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D90" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E90" s="31"/>
+      <c r="F90" s="31"/>
+      <c r="G90" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H90" s="46"/>
       <c r="I90" s="54"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A91" s="53"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="31"/>
-      <c r="D91" s="31"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="31"/>
+      <c r="A91" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B91" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C91" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D91" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E91" s="31"/>
+      <c r="F91" s="31"/>
+      <c r="G91" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H91" s="46"/>
       <c r="I91" s="54"/>
     </row>
     <row r="92" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="53"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="31"/>
-      <c r="D92" s="31"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="31"/>
+      <c r="A92" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B92" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C92" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D92" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E92" s="31"/>
+      <c r="F92" s="31"/>
+      <c r="G92" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H92" s="46"/>
       <c r="I92" s="54"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" s="53"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="31"/>
-      <c r="D93" s="31"/>
-      <c r="E93" s="30"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="31"/>
+      <c r="A93" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B93" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C93" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D93" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E93" s="31"/>
+      <c r="F93" s="31"/>
+      <c r="G93" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H93" s="46"/>
       <c r="I93" s="54"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" s="53"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="31"/>
-      <c r="D94" s="31"/>
-      <c r="E94" s="30"/>
-      <c r="F94" s="30"/>
-      <c r="G94" s="31"/>
+      <c r="A94" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B94" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C94" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D94" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E94" s="31"/>
+      <c r="F94" s="31"/>
+      <c r="G94" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="H94" s="46"/>
       <c r="I94" s="54"/>
     </row>
     <row r="95" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="55"/>
-      <c r="B95" s="56"/>
-      <c r="C95" s="57"/>
-      <c r="D95" s="57"/>
-      <c r="E95" s="58"/>
-      <c r="F95" s="58"/>
-      <c r="G95" s="57"/>
-      <c r="H95" s="60"/>
-      <c r="I95" s="59"/>
+      <c r="A95" s="53" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B95" s="29" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="C95" s="31" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="D95" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E95" s="31"/>
+      <c r="F95" s="31"/>
+      <c r="G95" s="31" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H95" s="56"/>
+      <c r="I95" s="55"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E100" s="9"/>
@@ -26175,6 +27461,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007936CBEE0A456044BDA65122A5B0F5F8" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5d7b9cbce9364425416f89c8d3c2b0fb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0a16e579-8e52-462c-b9fb-90fad13862ef" xmlns:ns3="f2e3cb03-81f0-44cd-9968-695b701ef7ef" xmlns:ns4="90a9caed-1441-4e6e-970c-7f1ae8660165" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ac0bef3ad4cc5a6152d7bbfb167c93" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="0a16e579-8e52-462c-b9fb-90fad13862ef"/>
@@ -26440,15 +27735,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A12C31FE-0938-4A9D-97BC-C84B277439DE}">
   <ds:schemaRefs>
@@ -26468,6 +27754,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86B748C9-2DB3-4ACB-B82C-358346E88931}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0F463A-F08C-4278-B826-D14456484583}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26485,12 +27779,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86B748C9-2DB3-4ACB-B82C-358346E88931}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>